--- a/balance_tables/战斗规则.xlsx
+++ b/balance_tables/战斗规则.xlsx
@@ -421,7 +421,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="CombatRulesTable" displayName="CombatRulesTable" ref="A3:E4" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="CombatRulesTable" displayName="CombatRulesTable" ref="A3:E10" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <tableColumns count="5">
     <tableColumn id="1" name="参数ID"/>
     <tableColumn id="2" name="显示名称"/>
@@ -717,7 +717,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -783,6 +783,156 @@
       <c r="E4" s="35" t="inlineStr">
         <is>
           <t>每次实际受击后，忽略后续伤害的持续时间；必须大于 0。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>respawn_base_seconds</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>多人复活基础时间</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>15</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>秒</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>多人局第一次死亡的复活等待时间。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>respawn_increment_seconds</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>多人复活递增时间</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>15</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>秒</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>每次死亡后增加的复活等待时间。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>respawn_max_seconds</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>多人复活时间上限</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>180</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>秒</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>复活等待时间的最高值。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>ghost_damage_multiplier</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>幽灵车输出倍率</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>倍率</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>幽灵车仍可移动、攻击和领取成长，但输出降为正常值的1%。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>respawn_durability_ratio</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>复活初始耐久比例</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>比例</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>复活时先按最终最大耐久的该比例恢复。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>respawn_invincibility_seconds</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>复活保护时间</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>2</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>秒</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>复活后免受敌人伤害的保护时间。</t>
         </is>
       </c>
     </row>
@@ -852,7 +1002,7 @@
         </is>
       </c>
       <c r="B3" s="47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3" s="48" t="inlineStr">
         <is>
